--- a/templates_formats/cronograma.xlsx
+++ b/templates_formats/cronograma.xlsx
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -191,28 +191,13 @@
       <alignment horizontal="left" indent="12"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="13"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="15"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="17"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="16"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="19"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -226,14 +211,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="19"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="16"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="23"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="18"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -634,70 +622,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:L66"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.25" customWidth="1"/>
-    <col min="2" max="2" width="3.125" customWidth="1"/>
-    <col min="3" max="3" width="11.75" customWidth="1"/>
+    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="2" max="2" width="8.875" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
     <col min="4" max="4" width="28.75" customWidth="1"/>
     <col min="5" max="5" width="22.75" customWidth="1"/>
-    <col min="6" max="6" width="10.25" customWidth="1"/>
-    <col min="7" max="7" width="8.375" customWidth="1"/>
-    <col min="8" max="8" width="25.875" customWidth="1"/>
+    <col min="6" max="6" width="4.75" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="8.125" customWidth="1"/>
     <col min="9" max="9" width="5.75" customWidth="1"/>
     <col min="10" max="10" width="2.5" customWidth="1"/>
     <col min="11" max="11" width="8.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C1" s="19" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C2" s="20" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="10" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="5" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="3"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="13" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D6" s="5"/>
       <c r="E6" s="3"/>
       <c r="G6" s="2"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C7" s="2"/>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -705,12 +722,12 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C8" s="2"/>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="2"/>
@@ -719,12 +736,12 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C9" s="2"/>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="2"/>
@@ -733,174 +750,174 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D11" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D13" s="12" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D13" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D14" s="14" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D14" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="12"/>
     </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D15" s="14" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D15" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="12"/>
     </row>
-    <row r="16" spans="3:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="D16" s="14" t="s">
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="D16" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="12"/>
     </row>
     <row r="17" spans="4:5" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="12"/>
     </row>
     <row r="18" spans="4:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="12"/>
     </row>
     <row r="19" spans="4:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="12"/>
     </row>
     <row r="20" spans="4:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="12"/>
     </row>
     <row r="21" spans="4:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="12"/>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="12"/>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="12"/>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="12"/>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="12"/>
     </row>
     <row r="26" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D26" s="14"/>
-      <c r="E26" s="12"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="14"/>
-      <c r="E27" s="12"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D28" s="14"/>
-      <c r="E28" s="12"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="14"/>
-      <c r="E29" s="12"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="15"/>
+      <c r="D30" s="10"/>
     </row>
     <row r="31" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D31" s="15"/>
+      <c r="D31" s="10"/>
     </row>
     <row r="32" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D32" s="15"/>
+      <c r="D32" s="10"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="15"/>
+      <c r="D33" s="10"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D34" s="15"/>
+      <c r="D34" s="10"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="15"/>
+      <c r="D35" s="10"/>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" s="15"/>
+      <c r="D36" s="10"/>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D37" s="15"/>
+      <c r="D37" s="10"/>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D38" s="15"/>
+      <c r="D38" s="10"/>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D39" s="15"/>
+      <c r="D39" s="10"/>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D40" s="15"/>
+      <c r="D40" s="10"/>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D41" s="15"/>
+      <c r="D41" s="10"/>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D42" s="15"/>
+      <c r="D42" s="10"/>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D43" s="15"/>
+      <c r="D43" s="10"/>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D44" s="15"/>
+      <c r="D44" s="10"/>
     </row>
     <row r="45" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D45" s="15"/>
+      <c r="D45" s="10"/>
     </row>
     <row r="46" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D46" s="15"/>
+      <c r="D46" s="10"/>
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D47" s="15"/>
+      <c r="D47" s="10"/>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D48" s="15"/>
+      <c r="D48" s="10"/>
     </row>
     <row r="49" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D49" s="15"/>
+      <c r="D49" s="10"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
     <row r="50" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D50" s="15"/>
+      <c r="D50" s="10"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
@@ -970,8 +987,13 @@
       <c r="L66" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="172" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -980,73 +1002,91 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:J30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="3" width="3.125" customWidth="1"/>
     <col min="4" max="4" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="19" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C2" s="20" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="8"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="10" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C4" s="5" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="11"/>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C5" s="13" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D6" s="5"/>
       <c r="E6" s="3"/>
       <c r="G6" s="2"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D7" s="18" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D9" s="10" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D9" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="2"/>
@@ -1054,187 +1094,215 @@
       <c r="I9" s="2"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D11" s="17" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D11" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D12" s="16" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="17"/>
-    </row>
-    <row r="13" spans="3:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="D13" s="16" t="s">
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="17"/>
-    </row>
-    <row r="14" spans="3:10" ht="105" x14ac:dyDescent="0.25">
-      <c r="D14" s="16" t="s">
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="D14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="17"/>
-    </row>
-    <row r="15" spans="3:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="D15" s="16" t="s">
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="17"/>
-    </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D16" s="16" t="s">
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="17"/>
+      <c r="E16" s="12"/>
     </row>
     <row r="17" spans="4:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="17"/>
+      <c r="E17" s="12"/>
     </row>
     <row r="18" spans="4:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="17"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="17"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="17"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="16"/>
-      <c r="E23" s="17"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="16"/>
-      <c r="E24" s="17"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D26" s="16"/>
-      <c r="E26" s="17"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="12"/>
     </row>
     <row r="27" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="16"/>
-      <c r="E27" s="17"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="12"/>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D28" s="16"/>
-      <c r="E28" s="17"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="16"/>
-      <c r="E29" s="17"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="12"/>
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="16"/>
-      <c r="E30" s="17"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="D1:J209"/>
+  <dimension ref="A1:J209"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="4.25" customWidth="1"/>
     <col min="4" max="4" width="27.75" customWidth="1"/>
     <col min="5" max="5" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D1" s="19" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D2" s="20" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="8"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="10" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D4" s="5" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D5" s="13" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D6" s="5"/>
       <c r="E6" s="3"/>
       <c r="G6" s="2"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D7" s="18" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D9" s="10" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D9" s="14" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="2"/>
@@ -1242,836 +1310,842 @@
       <c r="I9" s="2"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D11" s="16" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D11" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D12" s="16" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="16"/>
-    </row>
-    <row r="13" spans="4:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="D13" s="16" t="s">
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="16"/>
-    </row>
-    <row r="14" spans="4:10" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="16" t="s">
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:10" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="16"/>
-    </row>
-    <row r="15" spans="4:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="D15" s="16" t="s">
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D15" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="16"/>
-    </row>
-    <row r="16" spans="4:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="D16" s="16" t="s">
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="16"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="4:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="16"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="16"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="16"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="4:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="16"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="16"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="16"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
     </row>
     <row r="35" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
     </row>
     <row r="37" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
     </row>
     <row r="38" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
     </row>
     <row r="40" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
     </row>
     <row r="41" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
     </row>
     <row r="45" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
     </row>
     <row r="46" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
     </row>
     <row r="48" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
     </row>
     <row r="50" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
     </row>
     <row r="51" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
     </row>
     <row r="52" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
     </row>
     <row r="53" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
     </row>
     <row r="54" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
     </row>
     <row r="55" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
     </row>
     <row r="56" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
     </row>
     <row r="57" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
     </row>
     <row r="58" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
     </row>
     <row r="59" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
     </row>
     <row r="60" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
     </row>
     <row r="61" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
     </row>
     <row r="62" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
     </row>
     <row r="63" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
     </row>
     <row r="64" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
     </row>
     <row r="65" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
     </row>
     <row r="66" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
     </row>
     <row r="67" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
     </row>
     <row r="68" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
     </row>
     <row r="69" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
     </row>
     <row r="70" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
     </row>
     <row r="71" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
     </row>
     <row r="72" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
     </row>
     <row r="73" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
     </row>
     <row r="74" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
     </row>
     <row r="75" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
     </row>
     <row r="76" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
     </row>
     <row r="77" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
     </row>
     <row r="78" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
     </row>
     <row r="79" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
     </row>
     <row r="80" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
     </row>
     <row r="81" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
     </row>
     <row r="82" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D82" s="16"/>
-      <c r="E82" s="16"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
     </row>
     <row r="83" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
     </row>
     <row r="84" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D84" s="16"/>
-      <c r="E84" s="16"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
     </row>
     <row r="85" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D85" s="16"/>
-      <c r="E85" s="16"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
     </row>
     <row r="86" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D86" s="16"/>
-      <c r="E86" s="16"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
     </row>
     <row r="87" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D87" s="16"/>
-      <c r="E87" s="16"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
     </row>
     <row r="88" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
     </row>
     <row r="89" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
     </row>
     <row r="90" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D90" s="16"/>
-      <c r="E90" s="16"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
     </row>
     <row r="91" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
     </row>
     <row r="92" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D92" s="16"/>
-      <c r="E92" s="16"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
     </row>
     <row r="93" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D93" s="16"/>
-      <c r="E93" s="16"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
     </row>
     <row r="94" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D94" s="16"/>
-      <c r="E94" s="16"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
     </row>
     <row r="95" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D95" s="16"/>
-      <c r="E95" s="16"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
     </row>
     <row r="96" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D96" s="16"/>
-      <c r="E96" s="16"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
     </row>
     <row r="97" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D97" s="16"/>
-      <c r="E97" s="16"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
     </row>
     <row r="98" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D98" s="16"/>
-      <c r="E98" s="16"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
     </row>
     <row r="99" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D99" s="16"/>
-      <c r="E99" s="16"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
     </row>
     <row r="100" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D100" s="16"/>
-      <c r="E100" s="16"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
     </row>
     <row r="101" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D101" s="16"/>
-      <c r="E101" s="16"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
     </row>
     <row r="102" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D102" s="16"/>
-      <c r="E102" s="16"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
     </row>
     <row r="103" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D103" s="16"/>
-      <c r="E103" s="16"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
     </row>
     <row r="104" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D104" s="16"/>
-      <c r="E104" s="16"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
     </row>
     <row r="105" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D105" s="16"/>
-      <c r="E105" s="16"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
     </row>
     <row r="106" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D106" s="16"/>
-      <c r="E106" s="16"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
     </row>
     <row r="107" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D107" s="16"/>
-      <c r="E107" s="16"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
     </row>
     <row r="108" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D108" s="16"/>
-      <c r="E108" s="16"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
     </row>
     <row r="109" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D109" s="16"/>
-      <c r="E109" s="16"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
     </row>
     <row r="110" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D110" s="16"/>
-      <c r="E110" s="16"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
     </row>
     <row r="111" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D111" s="16"/>
-      <c r="E111" s="16"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
     </row>
     <row r="112" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D112" s="16"/>
-      <c r="E112" s="16"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
     </row>
     <row r="113" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D113" s="16"/>
-      <c r="E113" s="16"/>
+      <c r="D113" s="11"/>
+      <c r="E113" s="11"/>
     </row>
     <row r="114" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D114" s="16"/>
-      <c r="E114" s="16"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
     </row>
     <row r="115" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D115" s="16"/>
-      <c r="E115" s="16"/>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11"/>
     </row>
     <row r="116" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D116" s="16"/>
-      <c r="E116" s="16"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
     </row>
     <row r="117" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D117" s="16"/>
-      <c r="E117" s="16"/>
+      <c r="D117" s="11"/>
+      <c r="E117" s="11"/>
     </row>
     <row r="118" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D118" s="16"/>
-      <c r="E118" s="16"/>
+      <c r="D118" s="11"/>
+      <c r="E118" s="11"/>
     </row>
     <row r="119" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D119" s="16"/>
-      <c r="E119" s="16"/>
+      <c r="D119" s="11"/>
+      <c r="E119" s="11"/>
     </row>
     <row r="120" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D120" s="16"/>
-      <c r="E120" s="16"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
     </row>
     <row r="121" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D121" s="16"/>
-      <c r="E121" s="16"/>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
     </row>
     <row r="122" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D122" s="16"/>
-      <c r="E122" s="16"/>
+      <c r="D122" s="11"/>
+      <c r="E122" s="11"/>
     </row>
     <row r="123" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D123" s="16"/>
-      <c r="E123" s="16"/>
+      <c r="D123" s="11"/>
+      <c r="E123" s="11"/>
     </row>
     <row r="124" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D124" s="16"/>
-      <c r="E124" s="16"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
     </row>
     <row r="125" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D125" s="16"/>
-      <c r="E125" s="16"/>
+      <c r="D125" s="11"/>
+      <c r="E125" s="11"/>
     </row>
     <row r="126" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D126" s="16"/>
-      <c r="E126" s="16"/>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11"/>
     </row>
     <row r="127" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D127" s="16"/>
-      <c r="E127" s="16"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
     </row>
     <row r="128" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D128" s="16"/>
-      <c r="E128" s="16"/>
+      <c r="D128" s="11"/>
+      <c r="E128" s="11"/>
     </row>
     <row r="129" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D129" s="16"/>
-      <c r="E129" s="16"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
     </row>
     <row r="130" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D130" s="16"/>
-      <c r="E130" s="16"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="11"/>
     </row>
     <row r="131" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D131" s="16"/>
-      <c r="E131" s="16"/>
+      <c r="D131" s="11"/>
+      <c r="E131" s="11"/>
     </row>
     <row r="132" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D132" s="16"/>
-      <c r="E132" s="16"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
     </row>
     <row r="133" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D133" s="16"/>
-      <c r="E133" s="16"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
     </row>
     <row r="134" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D134" s="16"/>
-      <c r="E134" s="16"/>
+      <c r="D134" s="11"/>
+      <c r="E134" s="11"/>
     </row>
     <row r="135" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D135" s="16"/>
-      <c r="E135" s="16"/>
+      <c r="D135" s="11"/>
+      <c r="E135" s="11"/>
     </row>
     <row r="136" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D136" s="16"/>
-      <c r="E136" s="16"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
     </row>
     <row r="137" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D137" s="16"/>
-      <c r="E137" s="16"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
     </row>
     <row r="138" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D138" s="16"/>
-      <c r="E138" s="16"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
     </row>
     <row r="139" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D139" s="16"/>
-      <c r="E139" s="16"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
     </row>
     <row r="140" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D140" s="16"/>
-      <c r="E140" s="16"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="11"/>
     </row>
     <row r="141" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D141" s="16"/>
-      <c r="E141" s="16"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
     </row>
     <row r="142" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D142" s="16"/>
-      <c r="E142" s="16"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
     </row>
     <row r="143" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D143" s="16"/>
-      <c r="E143" s="16"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
     </row>
     <row r="144" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D144" s="16"/>
-      <c r="E144" s="16"/>
+      <c r="D144" s="11"/>
+      <c r="E144" s="11"/>
     </row>
     <row r="145" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D145" s="16"/>
-      <c r="E145" s="16"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
     </row>
     <row r="146" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D146" s="16"/>
-      <c r="E146" s="16"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
     </row>
     <row r="147" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D147" s="16"/>
-      <c r="E147" s="16"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
     </row>
     <row r="148" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D148" s="16"/>
-      <c r="E148" s="16"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
     </row>
     <row r="149" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D149" s="16"/>
-      <c r="E149" s="16"/>
+      <c r="D149" s="11"/>
+      <c r="E149" s="11"/>
     </row>
     <row r="150" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D150" s="16"/>
-      <c r="E150" s="16"/>
+      <c r="D150" s="11"/>
+      <c r="E150" s="11"/>
     </row>
     <row r="151" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D151" s="16"/>
-      <c r="E151" s="16"/>
+      <c r="D151" s="11"/>
+      <c r="E151" s="11"/>
     </row>
     <row r="152" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D152" s="16"/>
-      <c r="E152" s="16"/>
+      <c r="D152" s="11"/>
+      <c r="E152" s="11"/>
     </row>
     <row r="153" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D153" s="16"/>
-      <c r="E153" s="16"/>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11"/>
     </row>
     <row r="154" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D154" s="16"/>
-      <c r="E154" s="16"/>
+      <c r="D154" s="11"/>
+      <c r="E154" s="11"/>
     </row>
     <row r="155" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D155" s="16"/>
-      <c r="E155" s="16"/>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
     </row>
     <row r="156" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D156" s="16"/>
-      <c r="E156" s="16"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
     </row>
     <row r="157" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D157" s="16"/>
-      <c r="E157" s="16"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
     </row>
     <row r="158" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D158" s="16"/>
-      <c r="E158" s="16"/>
+      <c r="D158" s="11"/>
+      <c r="E158" s="11"/>
     </row>
     <row r="159" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D159" s="16"/>
-      <c r="E159" s="16"/>
+      <c r="D159" s="11"/>
+      <c r="E159" s="11"/>
     </row>
     <row r="160" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D160" s="16"/>
-      <c r="E160" s="16"/>
+      <c r="D160" s="11"/>
+      <c r="E160" s="11"/>
     </row>
     <row r="161" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D161" s="16"/>
-      <c r="E161" s="16"/>
+      <c r="D161" s="11"/>
+      <c r="E161" s="11"/>
     </row>
     <row r="162" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D162" s="16"/>
-      <c r="E162" s="16"/>
+      <c r="D162" s="11"/>
+      <c r="E162" s="11"/>
     </row>
     <row r="163" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D163" s="16"/>
-      <c r="E163" s="16"/>
+      <c r="D163" s="11"/>
+      <c r="E163" s="11"/>
     </row>
     <row r="164" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D164" s="16"/>
-      <c r="E164" s="16"/>
+      <c r="D164" s="11"/>
+      <c r="E164" s="11"/>
     </row>
     <row r="165" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D165" s="16"/>
-      <c r="E165" s="16"/>
+      <c r="D165" s="11"/>
+      <c r="E165" s="11"/>
     </row>
     <row r="166" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D166" s="16"/>
-      <c r="E166" s="16"/>
+      <c r="D166" s="11"/>
+      <c r="E166" s="11"/>
     </row>
     <row r="167" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D167" s="16"/>
-      <c r="E167" s="16"/>
+      <c r="D167" s="11"/>
+      <c r="E167" s="11"/>
     </row>
     <row r="168" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D168" s="16"/>
-      <c r="E168" s="16"/>
+      <c r="D168" s="11"/>
+      <c r="E168" s="11"/>
     </row>
     <row r="169" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D169" s="16"/>
-      <c r="E169" s="16"/>
+      <c r="D169" s="11"/>
+      <c r="E169" s="11"/>
     </row>
     <row r="170" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D170" s="16"/>
-      <c r="E170" s="16"/>
+      <c r="D170" s="11"/>
+      <c r="E170" s="11"/>
     </row>
     <row r="171" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D171" s="16"/>
-      <c r="E171" s="16"/>
+      <c r="D171" s="11"/>
+      <c r="E171" s="11"/>
     </row>
     <row r="172" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D172" s="16"/>
-      <c r="E172" s="16"/>
+      <c r="D172" s="11"/>
+      <c r="E172" s="11"/>
     </row>
     <row r="173" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D173" s="16"/>
-      <c r="E173" s="16"/>
+      <c r="D173" s="11"/>
+      <c r="E173" s="11"/>
     </row>
     <row r="174" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D174" s="16"/>
-      <c r="E174" s="16"/>
+      <c r="D174" s="11"/>
+      <c r="E174" s="11"/>
     </row>
     <row r="175" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D175" s="16"/>
-      <c r="E175" s="16"/>
+      <c r="D175" s="11"/>
+      <c r="E175" s="11"/>
     </row>
     <row r="176" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D176" s="16"/>
-      <c r="E176" s="16"/>
+      <c r="D176" s="11"/>
+      <c r="E176" s="11"/>
     </row>
     <row r="177" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D177" s="16"/>
-      <c r="E177" s="16"/>
+      <c r="D177" s="11"/>
+      <c r="E177" s="11"/>
     </row>
     <row r="178" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D178" s="16"/>
-      <c r="E178" s="16"/>
+      <c r="D178" s="11"/>
+      <c r="E178" s="11"/>
     </row>
     <row r="179" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D179" s="16"/>
-      <c r="E179" s="16"/>
+      <c r="D179" s="11"/>
+      <c r="E179" s="11"/>
     </row>
     <row r="180" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D180" s="16"/>
-      <c r="E180" s="16"/>
+      <c r="D180" s="11"/>
+      <c r="E180" s="11"/>
     </row>
     <row r="181" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D181" s="16"/>
-      <c r="E181" s="16"/>
+      <c r="D181" s="11"/>
+      <c r="E181" s="11"/>
     </row>
     <row r="182" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D182" s="16"/>
-      <c r="E182" s="16"/>
+      <c r="D182" s="11"/>
+      <c r="E182" s="11"/>
     </row>
     <row r="183" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D183" s="16"/>
-      <c r="E183" s="16"/>
+      <c r="D183" s="11"/>
+      <c r="E183" s="11"/>
     </row>
     <row r="184" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D184" s="16"/>
-      <c r="E184" s="16"/>
+      <c r="D184" s="11"/>
+      <c r="E184" s="11"/>
     </row>
     <row r="185" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D185" s="16"/>
-      <c r="E185" s="16"/>
+      <c r="D185" s="11"/>
+      <c r="E185" s="11"/>
     </row>
     <row r="186" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D186" s="16"/>
-      <c r="E186" s="16"/>
+      <c r="D186" s="11"/>
+      <c r="E186" s="11"/>
     </row>
     <row r="187" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D187" s="16"/>
-      <c r="E187" s="16"/>
+      <c r="D187" s="11"/>
+      <c r="E187" s="11"/>
     </row>
     <row r="188" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D188" s="16"/>
-      <c r="E188" s="16"/>
+      <c r="D188" s="11"/>
+      <c r="E188" s="11"/>
     </row>
     <row r="189" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D189" s="16"/>
-      <c r="E189" s="16"/>
+      <c r="D189" s="11"/>
+      <c r="E189" s="11"/>
     </row>
     <row r="190" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D190" s="16"/>
-      <c r="E190" s="16"/>
+      <c r="D190" s="11"/>
+      <c r="E190" s="11"/>
     </row>
     <row r="191" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D191" s="16"/>
-      <c r="E191" s="16"/>
+      <c r="D191" s="11"/>
+      <c r="E191" s="11"/>
     </row>
     <row r="192" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D192" s="16"/>
-      <c r="E192" s="16"/>
+      <c r="D192" s="11"/>
+      <c r="E192" s="11"/>
     </row>
     <row r="193" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D193" s="16"/>
-      <c r="E193" s="16"/>
+      <c r="D193" s="11"/>
+      <c r="E193" s="11"/>
     </row>
     <row r="194" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D194" s="16"/>
-      <c r="E194" s="16"/>
+      <c r="D194" s="11"/>
+      <c r="E194" s="11"/>
     </row>
     <row r="195" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D195" s="16"/>
-      <c r="E195" s="16"/>
+      <c r="D195" s="11"/>
+      <c r="E195" s="11"/>
     </row>
     <row r="196" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D196" s="16"/>
-      <c r="E196" s="16"/>
+      <c r="D196" s="11"/>
+      <c r="E196" s="11"/>
     </row>
     <row r="197" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D197" s="16"/>
-      <c r="E197" s="16"/>
+      <c r="D197" s="11"/>
+      <c r="E197" s="11"/>
     </row>
     <row r="198" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D198" s="16"/>
-      <c r="E198" s="16"/>
+      <c r="D198" s="11"/>
+      <c r="E198" s="11"/>
     </row>
     <row r="199" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D199" s="16"/>
-      <c r="E199" s="16"/>
+      <c r="D199" s="11"/>
+      <c r="E199" s="11"/>
     </row>
     <row r="200" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D200" s="16"/>
-      <c r="E200" s="16"/>
+      <c r="D200" s="11"/>
+      <c r="E200" s="11"/>
     </row>
     <row r="201" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D201" s="16"/>
-      <c r="E201" s="16"/>
+      <c r="D201" s="11"/>
+      <c r="E201" s="11"/>
     </row>
     <row r="202" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D202" s="16"/>
-      <c r="E202" s="16"/>
+      <c r="D202" s="11"/>
+      <c r="E202" s="11"/>
     </row>
     <row r="203" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D203" s="16"/>
-      <c r="E203" s="16"/>
+      <c r="D203" s="11"/>
+      <c r="E203" s="11"/>
     </row>
     <row r="204" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D204" s="16"/>
-      <c r="E204" s="16"/>
+      <c r="D204" s="11"/>
+      <c r="E204" s="11"/>
     </row>
     <row r="205" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D205" s="16"/>
-      <c r="E205" s="16"/>
+      <c r="D205" s="11"/>
+      <c r="E205" s="11"/>
     </row>
     <row r="206" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D206" s="16"/>
-      <c r="E206" s="16"/>
+      <c r="D206" s="11"/>
+      <c r="E206" s="11"/>
     </row>
     <row r="207" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D207" s="16"/>
-      <c r="E207" s="16"/>
+      <c r="D207" s="11"/>
+      <c r="E207" s="11"/>
     </row>
     <row r="208" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D208" s="16"/>
-      <c r="E208" s="16"/>
+      <c r="D208" s="11"/>
+      <c r="E208" s="11"/>
     </row>
     <row r="209" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D209" s="16"/>
-      <c r="E209" s="16"/>
+      <c r="D209" s="11"/>
+      <c r="E209" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/templates_formats/cronograma.xlsx
+++ b/templates_formats/cronograma.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-1875" yWindow="3930" windowWidth="15000" windowHeight="6555" activeTab="2"/>
+    <workbookView xWindow="-1875" yWindow="3930" windowWidth="15000" windowHeight="6555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,9 +63,6 @@
     <t>EVALUACION I MOMENTO MATERIA PENDIENTE</t>
   </si>
   <si>
-    <t>SEMANA ANIVERSARIO 28 DE OCTUBRE</t>
-  </si>
-  <si>
     <t>ENTREGA DE NOTAS AL DEPARTAMENTO DE EVALUACION</t>
   </si>
   <si>
@@ -127,6 +124,9 @@
   </si>
   <si>
     <t>"NOMBRE MUNICIPIO","NOMBRE ESTADO"</t>
+  </si>
+  <si>
+    <t>SEMANA ANIVERSARIO NOMBRE INSTITUTO</t>
   </si>
 </sst>
 </file>
@@ -640,7 +640,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -653,7 +653,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -679,7 +679,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -692,7 +692,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -798,43 +798,43 @@
     </row>
     <row r="19" spans="4:5" ht="30" x14ac:dyDescent="0.25">
       <c r="D19" s="9" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E19" s="12"/>
     </row>
     <row r="20" spans="4:5" ht="30" x14ac:dyDescent="0.25">
       <c r="D20" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20" s="12"/>
     </row>
     <row r="21" spans="4:5" ht="30" x14ac:dyDescent="0.25">
       <c r="D21" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" s="12"/>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D22" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="12"/>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D23" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" s="12"/>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D24" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" s="12"/>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D25" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="12"/>
     </row>
@@ -1012,7 +1012,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -1053,7 +1053,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -1119,43 +1119,43 @@
     </row>
     <row r="14" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="D14" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D15" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D16" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="12"/>
     </row>
     <row r="17" spans="4:5" ht="45" x14ac:dyDescent="0.25">
       <c r="D17" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" s="12"/>
     </row>
     <row r="18" spans="4:5" ht="30" x14ac:dyDescent="0.25">
       <c r="D18" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E18" s="12"/>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D19" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19" s="12"/>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D20" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" s="12"/>
     </row>
@@ -1227,7 +1227,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -1335,55 +1335,55 @@
     </row>
     <row r="14" spans="1:10" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D15" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D16" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" s="11"/>
     </row>
     <row r="17" spans="4:5" ht="30" x14ac:dyDescent="0.25">
       <c r="D17" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="11"/>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D18" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18" s="11"/>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D19" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" s="11"/>
     </row>
     <row r="20" spans="4:5" ht="45" x14ac:dyDescent="0.25">
       <c r="D20" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20" s="11"/>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D21" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="11"/>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D22" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" s="11"/>
     </row>
